--- a/tables/table-5-targeted-augmentation-results.xlsx
+++ b/tables/table-5-targeted-augmentation-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0574198c81a0fd8/ERP/moth-classification-research-project/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{D685D5E0-2F9C-4D34-8ADE-F737FDCAC0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A52D25C0-32D1-48FD-951B-6EA968CD8928}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{D685D5E0-2F9C-4D34-8ADE-F737FDCAC0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{502FCFE2-732E-4062-B0AE-AC8408D692C7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB7B5DEA-51D5-4375-A996-0E576EB78B9E}"/>
   </bookViews>
@@ -25,74 +25,118 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
   <si>
     <t>Architecture</t>
   </si>
   <si>
-    <t>Total Confused Pairs</t>
-  </si>
-  <si>
     <t>Training Time</t>
   </si>
   <si>
     <t>EfficientNet-B0</t>
   </si>
   <si>
-    <t>44 min 20 s</t>
-  </si>
-  <si>
     <t>MobileNetV2</t>
   </si>
   <si>
-    <t>40 min 54 s</t>
-  </si>
-  <si>
     <t>ViT-B/16</t>
   </si>
   <si>
-    <t>7 h 1 min 27 s</t>
-  </si>
-  <si>
     <t>CoaT-Lite Medium</t>
   </si>
   <si>
-    <t>3 h 16 min 55 s</t>
-  </si>
-  <si>
-    <t>Table 6: Targeted Augmentation Results</t>
-  </si>
-  <si>
-    <t>Standard Augmentations (%)</t>
-  </si>
-  <si>
-    <t>Targeted Augmentations (%)</t>
-  </si>
-  <si>
-    <t>Improvement (%)</t>
-  </si>
-  <si>
-    <t>- 0.4</t>
-  </si>
-  <si>
-    <t>- 2.8</t>
+    <t>Table A3 - Detailed Optimisation Pipeline Metrics</t>
+  </si>
+  <si>
+    <t>Stage</t>
+  </si>
+  <si>
+    <t>Accuracy (%)</t>
+  </si>
+  <si>
+    <t>Confused Pairs</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>23min 47s</t>
+  </si>
+  <si>
+    <t>16min 57s</t>
+  </si>
+  <si>
+    <t>14min 44s</t>
+  </si>
+  <si>
+    <t>44min 20s</t>
+  </si>
+  <si>
+    <t>3h 22min 9s</t>
+  </si>
+  <si>
+    <t>54min 19s</t>
+  </si>
+  <si>
+    <t>14min 1s</t>
+  </si>
+  <si>
+    <t>16min 40s</t>
+  </si>
+  <si>
+    <t>40min 54s</t>
+  </si>
+  <si>
+    <t>2h 35min 43s</t>
+  </si>
+  <si>
+    <t>299min 8s</t>
+  </si>
+  <si>
+    <t>3h 0min 3s</t>
+  </si>
+  <si>
+    <t>3h 9min 42s</t>
+  </si>
+  <si>
+    <t>7h 1min 27s</t>
+  </si>
+  <si>
+    <t>22h 35min 14s</t>
+  </si>
+  <si>
+    <t>55min 4s</t>
+  </si>
+  <si>
+    <t>1h 30min 14s</t>
+  </si>
+  <si>
+    <t>1h 42min 30s</t>
+  </si>
+  <si>
+    <t>3h 16min 55s</t>
+  </si>
+  <si>
+    <t>14h 43min 5s</t>
+  </si>
+  <si>
+    <t>+ Standard Augmentations</t>
+  </si>
+  <si>
+    <t>+ Targeted Augmentations</t>
+  </si>
+  <si>
+    <t>+ Fine-Tuning</t>
+  </si>
+  <si>
+    <t>+ CutMix</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,7 +172,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -151,55 +195,57 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -511,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF7F924F-61FC-4A99-8849-6A59E5D98BD1}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
@@ -519,122 +565,345 @@
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" customWidth="1"/>
     <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2">
+        <v>98.4</v>
+      </c>
+      <c r="D3" s="2">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-    </row>
-    <row r="2" spans="1:6" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2">
+        <v>98.8</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2">
+        <v>98</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="2">
+        <v>97.6</v>
+      </c>
+      <c r="D6" s="2">
+        <v>6</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="8">
+        <v>99.6</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="10">
+        <v>98.8</v>
+      </c>
+      <c r="D8" s="10">
+        <v>3</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2">
+        <v>98</v>
+      </c>
+      <c r="D9" s="2">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="B10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2">
+        <v>99.2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2">
+        <v>98.8</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="8">
+        <v>100</v>
+      </c>
+      <c r="D12" s="8">
         <v>0</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="E12" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="10">
+        <v>97.2</v>
+      </c>
+      <c r="D13" s="10">
+        <v>4</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="2">
+        <v>99.2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="2">
+        <v>98.8</v>
+      </c>
+      <c r="D15" s="2">
+        <v>3</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="2">
+        <v>98.4</v>
+      </c>
+      <c r="D16" s="2">
         <v>1</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="E16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="8">
+        <v>100</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2">
+        <v>97.6</v>
+      </c>
+      <c r="D18" s="2">
+        <v>4</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="2">
+        <v>98.8</v>
+      </c>
+      <c r="D19" s="2">
         <v>3</v>
       </c>
-      <c r="B3" s="10">
+      <c r="E19" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="2">
         <v>98</v>
       </c>
-      <c r="C3" s="10">
-        <v>97.6</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="6">
-        <v>6</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="D20" s="2">
         <v>5</v>
       </c>
-      <c r="B4" s="10">
-        <v>99.2</v>
-      </c>
-      <c r="C4" s="10">
-        <v>98.8</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="E20" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="2">
+        <v>95.2</v>
+      </c>
+      <c r="D21" s="2">
         <v>7</v>
       </c>
-      <c r="B5" s="10">
-        <v>98.8</v>
-      </c>
-      <c r="C5" s="10">
-        <v>98.4</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="E21" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="3">
+        <v>99.6</v>
+      </c>
+      <c r="D22" s="3">
         <v>1</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="11">
-        <v>98</v>
-      </c>
-      <c r="C6" s="11">
-        <v>95.2</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="3">
-        <v>7</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>10</v>
+      <c r="E22" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
